--- a/data/acervo_hsia_atualizado.xlsx
+++ b/data/acervo_hsia_atualizado.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Publicações" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Volumetria" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Histórico" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Publicações" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Volumetria" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Histórico" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Publicações'!$A$1:$AB$503</definedName>

--- a/data/acervo_hsia_atualizado.xlsx
+++ b/data/acervo_hsia_atualizado.xlsx
@@ -12,9 +12,9 @@
     <sheet name="Histórico" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Publicações'!$A$1:$AB$503</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Volumetria'!$A$1:$N$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Histórico'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Publicações'!$A$1:$AB$504</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Volumetria'!$A$1:$N$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Histórico'!$A$1:$G$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,14 +431,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB503"/>
+  <dimension ref="A1:AB504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
@@ -453,7 +453,7 @@
     <col width="48" customWidth="1" min="17" max="17"/>
     <col width="31" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
-    <col width="20" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="32" customWidth="1" min="22" max="22"/>
     <col width="38" customWidth="1" min="23" max="23"/>
@@ -71634,8 +71634,114 @@
         </is>
       </c>
     </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>TesteTesteTesteTeste</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>colunas_autorais</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>manifestacao-revisao-2dd3ee21-4ffa-4b55-9d92-ecac9ecae6a7</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>hsia-revisao-2dd3ee21-4ffa-4b55-9d92-ecac9ecae6a7</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>hsia-revisao-2dd3ee21-4ffa-4b55-9d92-ecac9ecae6a7</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr"/>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>origem</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>escrita</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>TesteTesteTesteTesteTesteTesteTesteTeste</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr"/>
+      <c r="L504" t="inlineStr"/>
+      <c r="M504" t="inlineStr"/>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>autor_unico</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>https://acervo-sheng.netlify.app/</t>
+        </is>
+      </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>https://acervo-sheng.netlify.app/</t>
+        </is>
+      </c>
+      <c r="Q504" t="inlineStr"/>
+      <c r="R504" t="inlineStr"/>
+      <c r="S504" t="inlineStr"/>
+      <c r="T504" t="inlineStr">
+        <is>
+          <t>confirmado_por_revisao</t>
+        </is>
+      </c>
+      <c r="U504" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="V504" t="inlineStr"/>
+      <c r="W504" t="inlineStr">
+        <is>
+          <t>a_verificar</t>
+        </is>
+      </c>
+      <c r="X504" t="inlineStr">
+        <is>
+          <t>evidencia_fornecida</t>
+        </is>
+      </c>
+      <c r="Y504" t="inlineStr"/>
+      <c r="Z504" t="inlineStr">
+        <is>
+          <t>Autoria</t>
+        </is>
+      </c>
+      <c r="AA504" t="inlineStr">
+        <is>
+          <t>Hsia Hua Sheng</t>
+        </is>
+      </c>
+      <c r="AB504" t="inlineStr">
+        <is>
+          <t>Autor ou coautor</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB503"/>
+  <autoFilter ref="A1:AB504"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -71646,7 +71752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -73040,16 +73146,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>The Economist</t>
+          <t>TesteTesteTesteTeste</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Site próprio</t>
+          <t>Link informado na revisão</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -73058,7 +73164,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -73076,23 +73182,21 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>reconciliacao_completa</t>
+          <t>incluido_por_revisao</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Touros e Ursos</t>
+          <t>The Economist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -73104,13 +73208,13 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -73122,13 +73226,13 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -73144,7 +73248,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TozziniFreire</t>
+          <t>Touros e Ursos</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -73156,7 +73260,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -73174,13 +73278,13 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -73196,19 +73300,19 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TV 247 / YouTube</t>
+          <t>TozziniFreire</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Site próprio</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -73232,7 +73336,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -73241,19 +73345,19 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>producao_adicional_verificada</t>
+          <t>reconciliacao_completa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Valor Economico</t>
+          <t>TV 247 / YouTube</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Site próprio</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -73266,25 +73370,25 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -73293,19 +73397,19 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>cobertura_superior</t>
+          <t>producao_adicional_verificada</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Xinhua</t>
+          <t>Valor Economico</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Material a fornecer</t>
+          <t>Site próprio</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -73315,16 +73419,16 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -73336,21 +73440,73 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
+        <v>11</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>cobertura_superior</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Xinhua</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Material a fornecer</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
         <v>1</v>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>aguardando_material_fornecido</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N32"/>
+  <autoFilter ref="A1:N33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -73361,16 +73517,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -73410,8 +73566,45 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-08-25T23:41:36.528Z</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>manifestacao-revisao-2dd3ee21-4ffa-4b55-9d92-ecac9ecae6a7</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>hsia-revisao-2dd3ee21-4ffa-4b55-9d92-ecac9ecae6a7</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>TesteTesteTesteTesteTesteTesteTesteTeste</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>TesteTesteTesteTeste</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:G2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/acervo_hsia_atualizado.xlsx
+++ b/data/acervo_hsia_atualizado.xlsx
@@ -12,9 +12,9 @@
     <sheet name="Histórico" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Publicações'!$A$1:$AB$504</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Volumetria'!$A$1:$N$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Histórico'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Publicações'!$A$1:$AB$503</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Volumetria'!$A$1:$N$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Histórico'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,14 +431,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB504"/>
+  <dimension ref="A1:AB503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
@@ -453,7 +453,7 @@
     <col width="48" customWidth="1" min="17" max="17"/>
     <col width="31" customWidth="1" min="18" max="18"/>
     <col width="25" customWidth="1" min="19" max="19"/>
-    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="32" customWidth="1" min="22" max="22"/>
     <col width="38" customWidth="1" min="23" max="23"/>
@@ -71634,114 +71634,8 @@
         </is>
       </c>
     </row>
-    <row r="504">
-      <c r="A504" t="inlineStr">
-        <is>
-          <t>TesteTesteTesteTeste</t>
-        </is>
-      </c>
-      <c r="B504" t="inlineStr">
-        <is>
-          <t>colunas_autorais</t>
-        </is>
-      </c>
-      <c r="C504" t="inlineStr">
-        <is>
-          <t>manifestacao-revisao-2dd3ee21-4ffa-4b55-9d92-ecac9ecae6a7</t>
-        </is>
-      </c>
-      <c r="D504" t="inlineStr">
-        <is>
-          <t>hsia-revisao-2dd3ee21-4ffa-4b55-9d92-ecac9ecae6a7</t>
-        </is>
-      </c>
-      <c r="E504" t="inlineStr">
-        <is>
-          <t>hsia-revisao-2dd3ee21-4ffa-4b55-9d92-ecac9ecae6a7</t>
-        </is>
-      </c>
-      <c r="F504" t="inlineStr"/>
-      <c r="G504" t="inlineStr">
-        <is>
-          <t>origem</t>
-        </is>
-      </c>
-      <c r="H504" t="inlineStr">
-        <is>
-          <t>escrita</t>
-        </is>
-      </c>
-      <c r="I504" t="inlineStr">
-        <is>
-          <t>TesteTesteTesteTesteTesteTesteTesteTeste</t>
-        </is>
-      </c>
-      <c r="J504" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K504" t="inlineStr"/>
-      <c r="L504" t="inlineStr"/>
-      <c r="M504" t="inlineStr"/>
-      <c r="N504" t="inlineStr">
-        <is>
-          <t>autor_unico</t>
-        </is>
-      </c>
-      <c r="O504" t="inlineStr">
-        <is>
-          <t>https://acervo-sheng.netlify.app/</t>
-        </is>
-      </c>
-      <c r="P504" t="inlineStr">
-        <is>
-          <t>https://acervo-sheng.netlify.app/</t>
-        </is>
-      </c>
-      <c r="Q504" t="inlineStr"/>
-      <c r="R504" t="inlineStr"/>
-      <c r="S504" t="inlineStr"/>
-      <c r="T504" t="inlineStr">
-        <is>
-          <t>confirmado_por_revisao</t>
-        </is>
-      </c>
-      <c r="U504" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-      <c r="V504" t="inlineStr"/>
-      <c r="W504" t="inlineStr">
-        <is>
-          <t>a_verificar</t>
-        </is>
-      </c>
-      <c r="X504" t="inlineStr">
-        <is>
-          <t>evidencia_fornecida</t>
-        </is>
-      </c>
-      <c r="Y504" t="inlineStr"/>
-      <c r="Z504" t="inlineStr">
-        <is>
-          <t>Autoria</t>
-        </is>
-      </c>
-      <c r="AA504" t="inlineStr">
-        <is>
-          <t>Hsia Hua Sheng</t>
-        </is>
-      </c>
-      <c r="AB504" t="inlineStr">
-        <is>
-          <t>Autor ou coautor</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AB504"/>
+  <autoFilter ref="A1:AB503"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -71752,7 +71646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -73146,16 +73040,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TesteTesteTesteTeste</t>
+          <t>The Economist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Link informado na revisão</t>
+          <t>Site próprio</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -73164,7 +73058,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -73182,21 +73076,23 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>incluido_por_revisao</t>
+          <t>reconciliacao_completa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>The Economist</t>
+          <t>Touros e Ursos</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -73208,13 +73104,13 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -73226,13 +73122,13 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -73248,7 +73144,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Touros e Ursos</t>
+          <t>TozziniFreire</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -73260,7 +73156,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -73278,13 +73174,13 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -73300,19 +73196,19 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TozziniFreire</t>
+          <t>TV 247 / YouTube</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Site próprio</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -73336,7 +73232,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -73345,19 +73241,19 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>reconciliacao_completa</t>
+          <t>producao_adicional_verificada</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TV 247 / YouTube</t>
+          <t>Valor Economico</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>YouTube</t>
+          <t>Site próprio</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -73370,25 +73266,25 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -73397,19 +73293,19 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>producao_adicional_verificada</t>
+          <t>cobertura_superior</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Valor Economico</t>
+          <t>Xinhua</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Site próprio</t>
+          <t>Material a fornecer</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -73419,16 +73315,16 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
         <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>10</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -73440,73 +73336,21 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
-        <is>
-          <t>cobertura_superior</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Xinhua</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Material a fornecer</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
         <is>
           <t>aguardando_material_fornecido</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N33"/>
+  <autoFilter ref="A1:N32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -73517,7 +73361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -73603,8 +73447,45 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-08-25T23:42:52.388Z</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>manifestacao-revisao-2dd3ee21-4ffa-4b55-9d92-ecac9ecae6a7</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>hsia-revisao-2dd3ee21-4ffa-4b55-9d92-ecac9ecae6a7</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>TesteTesteTesteTesteTesteTesteTesteTeste</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>TesteTesteTesteTeste</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>